--- a/results/Int Task Remove ACC -0.3/Rando_10_permute.xlsx
+++ b/results/Int Task Remove ACC -0.3/Rando_10_permute.xlsx
@@ -440,827 +440,827 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.6416333124981006</v>
+        <v>0.6186895733760223</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.636668791258073</v>
+        <v>0.6158583362970835</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.6249374737677301</v>
+        <v>0.6200433843755467</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.6178435698392346</v>
+        <v>0.6308106274471473</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.6168961280142984</v>
+        <v>0.6308106274471473</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.6202961587332616</v>
+        <v>0.6285038304247512</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.6107940194942213</v>
+        <v>0.6114387891800255</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.6112003886688093</v>
+        <v>0.5977238808728457</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.6095843576410136</v>
+        <v>0.5977238808728457</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.5960246868760211</v>
+        <v>0.5922626405659517</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.5973119675003224</v>
+        <v>0.5913151987410153</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.5979362031196996</v>
+        <v>0.6071317687469866</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.598817114569413</v>
+        <v>0.5929035087791348</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.6083746957878059</v>
+        <v>0.6092666956333896</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.6215501741699514</v>
+        <v>0.6070375173820872</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.6137433274551145</v>
+        <v>0.590519092985645</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.6053676871002531</v>
+        <v>0.5914720790085166</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.5964842392826547</v>
+        <v>0.5792124199890102</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.5991325178297299</v>
+        <v>0.598584258256132</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.5991325178297299</v>
+        <v>0.5966893746062594</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.5959503535555557</v>
+        <v>0.5906094428779234</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.6347123054089194</v>
+        <v>0.5912281342993654</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.6387786665834352</v>
+        <v>0.5743199733221409</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.634058090052559</v>
+        <v>0.5733725314972045</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.6172480819128551</v>
+        <v>0.5773563457246842</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.6188363919509745</v>
+        <v>0.5661993660723013</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.6074781784476082</v>
+        <v>0.5881180445983496</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.6077902962572967</v>
+        <v>0.5884523391997792</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.5952057883069169</v>
+        <v>0.6066161583390075</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.5955234503145408</v>
+        <v>0.6075913211536204</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.5970895835609192</v>
+        <v>0.6025530826151202</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.6030697197264205</v>
+        <v>0.6009425957852597</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.6030697197264205</v>
+        <v>0.5996774919526994</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.5979871276044383</v>
+        <v>0.6062652311437722</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.5998043924832175</v>
+        <v>0.6361880887630196</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.5803200275320763</v>
+        <v>0.6361880887630196</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.5968384519285185</v>
+        <v>0.6369636604519631</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.6007811980231443</v>
+        <v>0.6369636604519631</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.5816311276734327</v>
+        <v>0.6500027926330341</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.568747233034549</v>
+        <v>0.6499861600392283</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.5663810925601792</v>
+        <v>0.6499861600392283</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.5591707604750433</v>
+        <v>0.6756946058650222</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.5744296252368605</v>
+        <v>0.6630158465497429</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.5744296252368605</v>
+        <v>0.6676349847924704</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.5917575025318504</v>
+        <v>0.6803708288124164</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.5917575025318504</v>
+        <v>0.6804096381979632</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.6095116670458625</v>
+        <v>0.6856934641709289</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.6104923740584104</v>
+        <v>0.6814702227289118</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.6087820916657152</v>
+        <v>0.6780701920099483</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.6216953500195895</v>
+        <v>0.6783933982155075</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.6197450243903642</v>
+        <v>0.6783933982155075</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.619337012490462</v>
+        <v>0.6718888219934636</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.6294989112837981</v>
+        <v>0.6811414723254173</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.6301824903551489</v>
+        <v>0.6753863895279546</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.6083551884247004</v>
+        <v>0.6823749536956802</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.6416476863445995</v>
+        <v>0.6229138415213608</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.6449019251919319</v>
+        <v>0.6285730302286099</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.6416864957301462</v>
+        <v>0.635851535414283</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.6465528641326534</v>
+        <v>0.6253426108983325</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.6207351770734684</v>
+        <v>0.6220717394571943</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.6050383206747658</v>
+        <v>0.6227181518683126</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.6128285347957969</v>
+        <v>0.5555085097278086</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.6047262028650773</v>
+        <v>0.5104269935909072</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.5805506250980501</v>
+        <v>0.5287205880299535</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.5888320140880123</v>
+        <v>0.5011460062472843</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.5753815845564108</v>
+        <v>0.4976295473716805</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.5306643427579223</v>
+        <v>0.5155089696908965</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.5316450497704702</v>
+        <v>0.5116914814014747</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.5315801621205613</v>
+        <v>0.5147333980019532</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.5349397407286637</v>
+        <v>0.5074343587498531</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.5349397407286637</v>
+        <v>0.5096635370011556</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.5109986620002316</v>
+        <v>0.5283318781524926</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.5138132664853645</v>
+        <v>0.5276854657413743</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.5083464819805353</v>
+        <v>0.5433118902922326</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.5657313946984326</v>
+        <v>0.536384312301795</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.5592101858825829</v>
+        <v>0.5290575520600186</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.5633841455651756</v>
+        <v>0.5295692609953765</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.5203687671921471</v>
+        <v>0.5014147971768123</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.4880237110971845</v>
+        <v>0.4946424567285618</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.4886923003000438</v>
+        <v>0.4956453405328508</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.4946313683326913</v>
+        <v>0.4984544008200484</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.4710173972824395</v>
+        <v>0.4982808879587413</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.4794224013522915</v>
+        <v>0.498253166969065</v>
       </c>
     </row>
     <row r="85">
@@ -1270,57 +1270,57 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.4903964224728108</v>
+        <v>0.4901896444238921</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.4917058798888532</v>
+        <v>0.4983490610592786</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.4920900722717002</v>
+        <v>0.501898785122494</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.5027852407701424</v>
+        <v>0.5024287693769718</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.5059674050443166</v>
+        <v>0.5024287693769718</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.5013981645830065</v>
+        <v>0.5050421400111212</v>
       </c>
     </row>
   </sheetData>
